--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-coverage.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>The Coverage resource contains the insurance card level information, which is customary to provide on claims and other communications between providers and insurers.  
-Coverageには、保険証レベルの情報が含まれている。これは、保険金請求やプロバイダと保険会社間のその他の通信で提供するのが通例である。</t>
+Coverageには、保険証レベルの情報が含まれている。これは、保険金請求や医療提供者と保険会社間のその他の通信で提供するのが通例である。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -549,14 +549,14 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+    <t>Business Identifier for the coverage　この保険適用情報に割り当てられた一意の識別子【詳細参照】</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this coverage.  この保険適用情報に割り当てられた一意の識別子。</t>
   </si>
   <si>
     <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
+保険適用情報を区別して参照できるようにする。</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -826,7 +826,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"</t>
@@ -857,7 +857,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"
@@ -887,7 +887,7 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the coverage as not currently valid.  
-ステータスには、カバレッジが現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
+ステータスには、保険適用情報が現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
   </si>
   <si>
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.  
@@ -925,7 +925,7 @@
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
-カバレッジの適用順序は、カバレッジのタイプによって異なる。</t>
+保険適用の適用順序は、保険適用のタイプによって異なる。</t>
   </si>
   <si>
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  
@@ -1291,7 +1291,7 @@
   </si>
   <si>
     <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care.  
-現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、ナンバリングにギャップがある場合があり、カバーの具体的な位置づけはケアのエピソードに依存するため、一次、二次などを意味するものではない。</t>
+現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、採番にギャップがある場合があり、適用範囲の具体的な位置づけは診療エピソードに依存するため、一次、二次などを意味するものではない。</t>
   </si>
   <si>
     <t>32 bit number; for values larger than this, use decimal  
@@ -1310,7 +1310,7 @@
   </si>
   <si>
     <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.  
-保険者が定義したプロバイダの保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
+保険者が定義した医療提供者の保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
   </si>
   <si>
     <t>Used in referral for treatment and in claims processing.  
@@ -1472,8 +1472,7 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size  
-自己負担率を表すコード　"copaypct"</t>
+    <t>自己負担率を表すコード　"copaypct"</t>
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-coverage.xlsx
@@ -920,7 +920,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
+すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。  
 【JP Core仕様】「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」等で使用される保険種別コード（system=”http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber”）として、https://www.mhlw.go.jp/content/10800000/000342368.pdf　の別表１１が使用している例があげられている。JP Coreとして本項目に対する用語のバインドは現時点では定義するまでに至っていない。</t>
   </si>
   <si>
@@ -947,7 +947,7 @@
 </t>
   </si>
   <si>
-    <t>Owner of the policy　ポリシの所有者</t>
+    <t>Owner of the policy　ポリシーの所有者</t>
   </si>
   <si>
     <t>The party who 'owns' the insurance policy.  
@@ -959,7 +959,7 @@
   </si>
   <si>
     <t>This provides employer information in the case of Worker's Compensation and other policies.  
-これは、労働者災害補償およびその他のポリシの場合に雇用者情報を提供する。</t>
+これは、労働者災害補償およびその他のポリシーの場合に雇用者情報を提供する。</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
@@ -985,7 +985,7 @@
   </si>
   <si>
     <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.  
-ポリシにサインアップした、またはポリシとの契約関係を「所有」している当事者、またはポリシの利益が彼らまたはその家族に提供されることになっている当事者。</t>
+ポリシーにサインアップした、またはポリシーとの契約関係を「所有」している当事者、またはポリシーの利益が彼らまたはその家族に提供されることになっている当事者。</t>
   </si>
   <si>
     <t>May be self or a parent in the case of dependents.  
@@ -993,7 +993,7 @@
   </si>
   <si>
     <t>This is the party who is entitled to the benefits under the policy.  
-これは、ポリシに基づいて給付を受ける権利を有する当事者である。</t>
+これは、ポリシーに基づいて給付を受ける権利を有する当事者である。</t>
   </si>
   <si>
     <t>Coverage.subscriberId</t>
@@ -1078,7 +1078,7 @@
   </si>
   <si>
     <t>Typically, an individual uses policies which are theirs (relationship='self') before policies owned by others.  
-一般的に、個人は、他人が所有するポリシよりも、自分のポリシ（relationship='self'）を使用する。</t>
+一般的に、個人は、他人が所有するポリシーよりも、自分のポリシー（relationship='self'）を使用する。</t>
   </si>
   <si>
     <t>To determine relationship between the patient and the subscriber to determine coordination of benefits.  
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用し、テキスト、`Coding`、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  
@@ -1300,7 +1300,7 @@
   <si>
     <t>Used in managing the coordination of benefits.  
 保険給付の調整管理に使用する。  
-【JP Core仕様】公費情報で本リソースを使用する場合で、複数の公費負担情報がある場合に、その適用順序番号を示す１，２，３．．．を設定する。</t>
+【JP Core仕様】公費情報で本リソースを使用する場合で、複数の公費負担情報がある場合に、その適用順序番号を示す１、２、３…を設定する。</t>
   </si>
   <si>
     <t>Coverage.network</t>
@@ -1331,7 +1331,7 @@
   </si>
   <si>
     <t>A suite of codes indicating the cost category and associated amount which have been detailed in the policy and may have been  included on the health card.  
-ポリシに詳細が記載されており、ヘルスカードに含まれている可能性のあるコストカテゴリと関連する金額を示す一連のコード。</t>
+ポリシーに詳細が記載されており、ヘルスカードに含まれている可能性のあるコストカテゴリと関連する金額を示す一連のコード。</t>
   </si>
   <si>
     <t>For example by knowing the patient visit co-pay, the provider can collect the amount prior to undertaking treatment.  
@@ -1667,7 +1667,7 @@
   </si>
   <si>
     <t>The policy(s) which constitute this insurance coverage.  
-この保険の適用範囲を構成するポリシ。</t>
+この保険の適用範囲を構成するポリシー。</t>
   </si>
   <si>
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolvable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.  
